--- a/exports/monthly_ledger_excel/STANDARD/ledger_2027-04.xlsx
+++ b/exports/monthly_ledger_excel/STANDARD/ledger_2027-04.xlsx
@@ -397,79 +397,79 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>id</v>
+        <v>ID</v>
       </c>
       <c r="B1" t="str">
-        <v>date</v>
+        <v>날짜</v>
       </c>
       <c r="C1" t="str">
-        <v>description</v>
+        <v>적요</v>
       </c>
       <c r="D1" t="str">
-        <v>vendor</v>
+        <v>거래처</v>
       </c>
       <c r="E1" t="str">
-        <v>debitAccount</v>
+        <v>차변계정</v>
       </c>
       <c r="F1" t="str">
-        <v>debitAccountId</v>
+        <v>차변ID</v>
       </c>
       <c r="G1" t="str">
-        <v>creditAccount</v>
+        <v>대변계정</v>
       </c>
       <c r="H1" t="str">
-        <v>creditAccountId</v>
+        <v>대변ID</v>
       </c>
       <c r="I1" t="str">
-        <v>amount</v>
+        <v>금액</v>
       </c>
       <c r="J1" t="str">
-        <v>vat</v>
+        <v>부가세</v>
       </c>
       <c r="K1" t="str">
-        <v>type</v>
+        <v>유형</v>
       </c>
       <c r="L1" t="str">
-        <v>status</v>
+        <v>상태</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>COLL-2027-3</v>
+        <v>REV-AR-2027-4</v>
       </c>
       <c r="B2" t="str">
-        <v>2027-04-14</v>
+        <v>2027-04-28</v>
       </c>
       <c r="C2" t="str">
-        <v>[수금] 외상매출금 회수</v>
+        <v>[SaaS] 구독매출 채권 인식 (유저: 389명)</v>
       </c>
       <c r="D2" t="str">
         <v>Global Customers</v>
       </c>
       <c r="E2" t="str">
-        <v>보통예금</v>
+        <v>외상매출금</v>
       </c>
       <c r="F2" t="str">
-        <v>acc_103</v>
+        <v>acc_108</v>
       </c>
       <c r="G2" t="str">
-        <v>외상매출금</v>
+        <v>상품매출</v>
       </c>
       <c r="H2" t="str">
-        <v>acc_108</v>
+        <v>acc_401</v>
       </c>
       <c r="I2">
-        <v>5865300</v>
+        <v>9312660</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>931266</v>
       </c>
       <c r="K2" t="str">
-        <v>Asset</v>
+        <v>Revenue</v>
       </c>
       <c r="L2" t="str">
         <v>Approved</v>
@@ -477,16 +477,16 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>REV-2027-4</v>
+        <v>REV-COL-2027-4</v>
       </c>
       <c r="B3" t="str">
         <v>2027-04-28</v>
       </c>
       <c r="C3" t="str">
-        <v>[SaaS] 구독매출 (유저: 176명)</v>
+        <v>[SETTLE] 매출 대금 회수 (회수율 85% 완료)</v>
       </c>
       <c r="D3" t="str">
-        <v>Global Customers</v>
+        <v>Payment Gateway</v>
       </c>
       <c r="E3" t="str">
         <v>보통예금</v>
@@ -495,16 +495,16 @@
         <v>acc_103</v>
       </c>
       <c r="G3" t="str">
-        <v>상품매출</v>
+        <v>외상매출금</v>
       </c>
       <c r="H3" t="str">
-        <v>acc_401</v>
+        <v>acc_108</v>
       </c>
       <c r="I3">
-        <v>7022400</v>
+        <v>8707337</v>
       </c>
       <c r="J3">
-        <v>702240</v>
+        <v>0</v>
       </c>
       <c r="K3" t="str">
         <v>Revenue</v>
@@ -515,13 +515,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>COGS-2027-4</v>
+        <v>COGS-AP-2027-4</v>
       </c>
       <c r="B4" t="str">
         <v>2027-04-28</v>
       </c>
       <c r="C4" t="str">
-        <v>[COGS] AI API 자부담 결제분</v>
+        <v>[COGS] AI API 비용 청구 (미지급)</v>
       </c>
       <c r="D4" t="str">
         <v>AWS/OpenAI</v>
@@ -533,16 +533,16 @@
         <v>acc_501</v>
       </c>
       <c r="G4" t="str">
-        <v>보통예금</v>
+        <v>미지급금</v>
       </c>
       <c r="H4" t="str">
-        <v>acc_103</v>
+        <v>acc_253</v>
       </c>
       <c r="I4">
-        <v>362560</v>
+        <v>801340</v>
       </c>
       <c r="J4">
-        <v>36256</v>
+        <v>80134</v>
       </c>
       <c r="K4" t="str">
         <v>Expense</v>
@@ -553,22 +553,22 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>PAY-2027-4</v>
+        <v>COGS-PAY-2027-4</v>
       </c>
       <c r="B5" t="str">
         <v>2027-04-28</v>
       </c>
       <c r="C5" t="str">
-        <v>[PAY] 정기 인건비</v>
+        <v>[SETTLE] AI API 비용 결제 완료</v>
       </c>
       <c r="D5" t="str">
-        <v>Staff</v>
+        <v>AWS/OpenAI</v>
       </c>
       <c r="E5" t="str">
-        <v>급여</v>
+        <v>미지급금</v>
       </c>
       <c r="F5" t="str">
-        <v>acc_801</v>
+        <v>acc_253</v>
       </c>
       <c r="G5" t="str">
         <v>보통예금</v>
@@ -577,13 +577,13 @@
         <v>acc_103</v>
       </c>
       <c r="I5">
-        <v>6250000</v>
+        <v>881474</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5" t="str">
-        <v>Payroll</v>
+        <v>Expense</v>
       </c>
       <c r="L5" t="str">
         <v>Approved</v>
@@ -591,22 +591,22 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>MKT-2027-4</v>
+        <v>PAY-2027-4</v>
       </c>
       <c r="B6" t="str">
         <v>2027-04-28</v>
       </c>
       <c r="C6" t="str">
-        <v>[MKT] 마케팅비</v>
+        <v>[PAY] 정기 인건비</v>
       </c>
       <c r="D6" t="str">
-        <v>Google</v>
+        <v>Staff</v>
       </c>
       <c r="E6" t="str">
-        <v>마케팅비</v>
+        <v>급여</v>
       </c>
       <c r="F6" t="str">
-        <v>acc_830</v>
+        <v>acc_801</v>
       </c>
       <c r="G6" t="str">
         <v>보통예금</v>
@@ -615,21 +615,211 @@
         <v>acc_103</v>
       </c>
       <c r="I6">
+        <v>8190000</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Payroll</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>OH-2027-4</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2027-04-28</v>
+      </c>
+      <c r="C7" t="str">
+        <v>[EXP] 인건비 부대비용</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Staff Overhead</v>
+      </c>
+      <c r="E7" t="str">
+        <v>세금과공과</v>
+      </c>
+      <c r="F7" t="str">
+        <v>acc_817</v>
+      </c>
+      <c r="G7" t="str">
+        <v>보통예금</v>
+      </c>
+      <c r="H7" t="str">
+        <v>acc_103</v>
+      </c>
+      <c r="I7">
+        <v>1498770</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>RENT-AP-2027-4</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2027-04-28</v>
+      </c>
+      <c r="C8" t="str">
+        <v>[RENT] 공간 임차료 청구</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Bldg</v>
+      </c>
+      <c r="E8" t="str">
+        <v>임차료</v>
+      </c>
+      <c r="F8" t="str">
+        <v>acc_816</v>
+      </c>
+      <c r="G8" t="str">
+        <v>미지급금</v>
+      </c>
+      <c r="H8" t="str">
+        <v>acc_253</v>
+      </c>
+      <c r="I8">
+        <v>1560000</v>
+      </c>
+      <c r="J8">
+        <v>156000</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>RENT-PAY-2027-4</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2027-04-28</v>
+      </c>
+      <c r="C9" t="str">
+        <v>[SETTLE] 임차료 결제 (90%)</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Bldg</v>
+      </c>
+      <c r="E9" t="str">
+        <v>미지급금</v>
+      </c>
+      <c r="F9" t="str">
+        <v>acc_253</v>
+      </c>
+      <c r="G9" t="str">
+        <v>보통예금</v>
+      </c>
+      <c r="H9" t="str">
+        <v>acc_103</v>
+      </c>
+      <c r="I9">
+        <v>1544400</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>MKT-AP-2027-4</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2027-04-28</v>
+      </c>
+      <c r="C10" t="str">
+        <v>[MKT] 마케팅비 청구</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Google/FB</v>
+      </c>
+      <c r="E10" t="str">
+        <v>광고선전비</v>
+      </c>
+      <c r="F10" t="str">
+        <v>acc_826</v>
+      </c>
+      <c r="G10" t="str">
+        <v>미지급금</v>
+      </c>
+      <c r="H10" t="str">
+        <v>acc_253</v>
+      </c>
+      <c r="I10">
         <v>4160000</v>
       </c>
-      <c r="J6">
+      <c r="J10">
         <v>416000</v>
       </c>
-      <c r="K6" t="str">
+      <c r="K10" t="str">
         <v>Expense</v>
       </c>
-      <c r="L6" t="str">
+      <c r="L10" t="str">
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>MKT-PAY-2027-4</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2027-04-28</v>
+      </c>
+      <c r="C11" t="str">
+        <v>[SETTLE] 마케팅비 결제 (80% 우선집행)</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Google/FB</v>
+      </c>
+      <c r="E11" t="str">
+        <v>미지급금</v>
+      </c>
+      <c r="F11" t="str">
+        <v>acc_253</v>
+      </c>
+      <c r="G11" t="str">
+        <v>보통예금</v>
+      </c>
+      <c r="H11" t="str">
+        <v>acc_103</v>
+      </c>
+      <c r="I11">
+        <v>3660800</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="L11" t="str">
         <v>Approved</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/exports/monthly_ledger_excel/STANDARD/ledger_2027-04.xlsx
+++ b/exports/monthly_ledger_excel/STANDARD/ledger_2027-04.xlsx
@@ -439,34 +439,34 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>REV-AR-2027-4</v>
+        <v>AR-COLLECT-2027-4</v>
       </c>
       <c r="B2" t="str">
-        <v>2027-04-28</v>
+        <v>2027-04-05</v>
       </c>
       <c r="C2" t="str">
-        <v>[SaaS] 구독매출 채권 인식 (유저: 389명)</v>
+        <v>[SETTLE] 전월 매출 대금 회수 완료 (카드/PG 정산)</v>
       </c>
       <c r="D2" t="str">
-        <v>Global Customers</v>
+        <v>Payment Gateway</v>
       </c>
       <c r="E2" t="str">
+        <v>보통예금</v>
+      </c>
+      <c r="F2" t="str">
+        <v>acc_103</v>
+      </c>
+      <c r="G2" t="str">
         <v>외상매출금</v>
       </c>
-      <c r="F2" t="str">
+      <c r="H2" t="str">
         <v>acc_108</v>
       </c>
-      <c r="G2" t="str">
-        <v>상품매출</v>
-      </c>
-      <c r="H2" t="str">
-        <v>acc_401</v>
-      </c>
       <c r="I2">
-        <v>9312660</v>
+        <v>9348570</v>
       </c>
       <c r="J2">
-        <v>931266</v>
+        <v>0</v>
       </c>
       <c r="K2" t="str">
         <v>Revenue</v>
@@ -477,37 +477,37 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>REV-COL-2027-4</v>
+        <v>RENT-PAID-2027-4</v>
       </c>
       <c r="B3" t="str">
-        <v>2027-04-28</v>
+        <v>2027-04-05</v>
       </c>
       <c r="C3" t="str">
-        <v>[SETTLE] 매출 대금 회수 (회수율 85% 완료)</v>
+        <v>[SETTLE] 전월 임차료 및 부가세 지급 완료</v>
       </c>
       <c r="D3" t="str">
-        <v>Payment Gateway</v>
+        <v>Bldg Management</v>
       </c>
       <c r="E3" t="str">
+        <v>미지급금</v>
+      </c>
+      <c r="F3" t="str">
+        <v>acc_253</v>
+      </c>
+      <c r="G3" t="str">
         <v>보통예금</v>
       </c>
-      <c r="F3" t="str">
+      <c r="H3" t="str">
         <v>acc_103</v>
       </c>
-      <c r="G3" t="str">
-        <v>외상매출금</v>
-      </c>
-      <c r="H3" t="str">
-        <v>acc_108</v>
-      </c>
       <c r="I3">
-        <v>8707337</v>
+        <v>1716000</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3" t="str">
-        <v>Revenue</v>
+        <v>Expense</v>
       </c>
       <c r="L3" t="str">
         <v>Approved</v>
@@ -515,34 +515,34 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>COGS-AP-2027-4</v>
+        <v>MKT-PAID-2027-4</v>
       </c>
       <c r="B4" t="str">
-        <v>2027-04-28</v>
+        <v>2027-04-05</v>
       </c>
       <c r="C4" t="str">
-        <v>[COGS] AI API 비용 청구 (미지급)</v>
+        <v>[SETTLE] 전월 마케팅 집행 대금 결제 (Google/Meta)</v>
       </c>
       <c r="D4" t="str">
-        <v>AWS/OpenAI</v>
+        <v>Ad Agency</v>
       </c>
       <c r="E4" t="str">
-        <v>상품매출원가</v>
+        <v>미지급금</v>
       </c>
       <c r="F4" t="str">
-        <v>acc_501</v>
+        <v>acc_253</v>
       </c>
       <c r="G4" t="str">
-        <v>미지급금</v>
+        <v>보통예금</v>
       </c>
       <c r="H4" t="str">
-        <v>acc_253</v>
+        <v>acc_103</v>
       </c>
       <c r="I4">
-        <v>801340</v>
+        <v>4576000</v>
       </c>
       <c r="J4">
-        <v>80134</v>
+        <v>0</v>
       </c>
       <c r="K4" t="str">
         <v>Expense</v>
@@ -553,16 +553,16 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>COGS-PAY-2027-4</v>
+        <v>COGS-PAID-2027-4</v>
       </c>
       <c r="B5" t="str">
-        <v>2027-04-28</v>
+        <v>2027-04-05</v>
       </c>
       <c r="C5" t="str">
-        <v>[SETTLE] AI API 비용 결제 완료</v>
+        <v>[SETTLE] 전월 인프라/API 사용료 결제 (AWS/OpenAI)</v>
       </c>
       <c r="D5" t="str">
-        <v>AWS/OpenAI</v>
+        <v>Infra Provider</v>
       </c>
       <c r="E5" t="str">
         <v>미지급금</v>
@@ -577,7 +577,7 @@
         <v>acc_103</v>
       </c>
       <c r="I5">
-        <v>881474</v>
+        <v>804430</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -591,37 +591,37 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>PAY-2027-4</v>
+        <v>REV-AR-2027-4</v>
       </c>
       <c r="B6" t="str">
         <v>2027-04-28</v>
       </c>
       <c r="C6" t="str">
-        <v>[PAY] 정기 인건비</v>
+        <v>[SaaS] 구독매출 인식 (유저: 389명)</v>
       </c>
       <c r="D6" t="str">
-        <v>Staff</v>
+        <v>Global Customers</v>
       </c>
       <c r="E6" t="str">
-        <v>급여</v>
+        <v>외상매출금</v>
       </c>
       <c r="F6" t="str">
-        <v>acc_801</v>
+        <v>acc_108</v>
       </c>
       <c r="G6" t="str">
-        <v>보통예금</v>
+        <v>상품매출</v>
       </c>
       <c r="H6" t="str">
-        <v>acc_103</v>
+        <v>acc_401</v>
       </c>
       <c r="I6">
-        <v>8190000</v>
+        <v>9312660</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>931266</v>
       </c>
       <c r="K6" t="str">
-        <v>Payroll</v>
+        <v>Revenue</v>
       </c>
       <c r="L6" t="str">
         <v>Approved</v>
@@ -629,34 +629,34 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>OH-2027-4</v>
+        <v>COGS-AP-2027-4</v>
       </c>
       <c r="B7" t="str">
         <v>2027-04-28</v>
       </c>
       <c r="C7" t="str">
-        <v>[EXP] 인건비 부대비용</v>
+        <v>[COGS] AI 인프라 사용료 (미지급)</v>
       </c>
       <c r="D7" t="str">
-        <v>Staff Overhead</v>
+        <v>AWS/OpenAI</v>
       </c>
       <c r="E7" t="str">
-        <v>세금과공과</v>
+        <v>상품매출원가</v>
       </c>
       <c r="F7" t="str">
-        <v>acc_817</v>
+        <v>acc_501</v>
       </c>
       <c r="G7" t="str">
-        <v>보통예금</v>
+        <v>미지급금</v>
       </c>
       <c r="H7" t="str">
-        <v>acc_103</v>
+        <v>acc_253</v>
       </c>
       <c r="I7">
-        <v>1498770</v>
+        <v>801340</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>80134</v>
       </c>
       <c r="K7" t="str">
         <v>Expense</v>
@@ -667,37 +667,37 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>RENT-AP-2027-4</v>
+        <v>PAY-2027-4</v>
       </c>
       <c r="B8" t="str">
         <v>2027-04-28</v>
       </c>
       <c r="C8" t="str">
-        <v>[RENT] 공간 임차료 청구</v>
+        <v>[PAY] 당월 급여 지급</v>
       </c>
       <c r="D8" t="str">
-        <v>Bldg</v>
+        <v>Staff</v>
       </c>
       <c r="E8" t="str">
-        <v>임차료</v>
+        <v>급여</v>
       </c>
       <c r="F8" t="str">
-        <v>acc_816</v>
+        <v>acc_801</v>
       </c>
       <c r="G8" t="str">
-        <v>미지급금</v>
+        <v>보통예금</v>
       </c>
       <c r="H8" t="str">
-        <v>acc_253</v>
+        <v>acc_103</v>
       </c>
       <c r="I8">
-        <v>1560000</v>
+        <v>8190000</v>
       </c>
       <c r="J8">
-        <v>156000</v>
+        <v>0</v>
       </c>
       <c r="K8" t="str">
-        <v>Expense</v>
+        <v>Payroll</v>
       </c>
       <c r="L8" t="str">
         <v>Approved</v>
@@ -705,22 +705,22 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>RENT-PAY-2027-4</v>
+        <v>OH-2027-4</v>
       </c>
       <c r="B9" t="str">
         <v>2027-04-28</v>
       </c>
       <c r="C9" t="str">
-        <v>[SETTLE] 임차료 결제 (90%)</v>
+        <v>[EXP] 4대보험 및 제세공과금</v>
       </c>
       <c r="D9" t="str">
-        <v>Bldg</v>
+        <v>Staff Overhead</v>
       </c>
       <c r="E9" t="str">
-        <v>미지급금</v>
+        <v>세금과공과</v>
       </c>
       <c r="F9" t="str">
-        <v>acc_253</v>
+        <v>acc_817</v>
       </c>
       <c r="G9" t="str">
         <v>보통예금</v>
@@ -729,7 +729,7 @@
         <v>acc_103</v>
       </c>
       <c r="I9">
-        <v>1544400</v>
+        <v>1498770</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -743,22 +743,22 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>MKT-AP-2027-4</v>
+        <v>RENT-AP-2027-4</v>
       </c>
       <c r="B10" t="str">
         <v>2027-04-28</v>
       </c>
       <c r="C10" t="str">
-        <v>[MKT] 마케팅비 청구</v>
+        <v>[RENT] 사무실 임차료 청구</v>
       </c>
       <c r="D10" t="str">
-        <v>Google/FB</v>
+        <v>Bldg</v>
       </c>
       <c r="E10" t="str">
-        <v>광고선전비</v>
+        <v>임차료</v>
       </c>
       <c r="F10" t="str">
-        <v>acc_826</v>
+        <v>acc_816</v>
       </c>
       <c r="G10" t="str">
         <v>미지급금</v>
@@ -767,10 +767,10 @@
         <v>acc_253</v>
       </c>
       <c r="I10">
-        <v>4160000</v>
+        <v>1560000</v>
       </c>
       <c r="J10">
-        <v>416000</v>
+        <v>156000</v>
       </c>
       <c r="K10" t="str">
         <v>Expense</v>
@@ -781,34 +781,34 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>MKT-PAY-2027-4</v>
+        <v>MKT-AP-2027-4</v>
       </c>
       <c r="B11" t="str">
         <v>2027-04-28</v>
       </c>
       <c r="C11" t="str">
-        <v>[SETTLE] 마케팅비 결제 (80% 우선집행)</v>
+        <v>[MKT] 마케팅 광고 집행비 인식</v>
       </c>
       <c r="D11" t="str">
-        <v>Google/FB</v>
+        <v>Ad Partners</v>
       </c>
       <c r="E11" t="str">
+        <v>광고선전비</v>
+      </c>
+      <c r="F11" t="str">
+        <v>acc_826</v>
+      </c>
+      <c r="G11" t="str">
         <v>미지급금</v>
       </c>
-      <c r="F11" t="str">
+      <c r="H11" t="str">
         <v>acc_253</v>
       </c>
-      <c r="G11" t="str">
-        <v>보통예금</v>
-      </c>
-      <c r="H11" t="str">
-        <v>acc_103</v>
-      </c>
       <c r="I11">
-        <v>3660800</v>
+        <v>4160000</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>416000</v>
       </c>
       <c r="K11" t="str">
         <v>Expense</v>
